--- a/計算機.xlsx
+++ b/計算機.xlsx
@@ -1,18 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuu26\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5ABE234-2763-4667-B177-8585C014C23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="data (2)" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet1" sheetId="2" r:id="rId6"/>
+    <sheet name="data (2)" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
   <si>
     <t>No.</t>
   </si>
@@ -162,65 +184,761 @@
     <t>1. +を入力してEnterを押下する</t>
   </si>
   <si>
-    <t>「答えは+足し算の結果」が表示される</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>1. -を入力してEnterを押下する</t>
   </si>
   <si>
-    <t>「答えは+引き算の結果」が表示される</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
     <t>1. *を入力してEnterを押下する</t>
   </si>
   <si>
-    <t>「答えは+掛け算の結果」が表示される</t>
-  </si>
-  <si>
     <t>/</t>
   </si>
   <si>
     <t>1. /を入力してEnterを押下する</t>
-  </si>
-  <si>
-    <t>「答えは+割り算の結果」が表示される</t>
   </si>
   <si>
     <t>「エラー：不正な値が入力されました」
 「演算記号（+, -, *, /）を入力してください。」
 が表示される</t>
+  </si>
+  <si>
+    <t>小数</t>
+    <rPh sb="0" eb="1">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>計算結果</t>
+    <rPh sb="0" eb="2">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を入力すると加算が実行される</t>
+    </r>
+    <rPh sb="10" eb="12">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を入力すると減算が実行される</t>
+    </r>
+    <rPh sb="7" eb="9">
+      <t>ゲンサン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を入力するとが乗算実行される</t>
+    </r>
+    <rPh sb="8" eb="10">
+      <t>ジョウザン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を入力すると除算が実行される</t>
+    </r>
+    <rPh sb="7" eb="9">
+      <t>ジョサン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>加算</t>
+    <rPh sb="0" eb="2">
+      <t>カサン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>減算</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンサン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>除算</t>
+    <rPh sb="0" eb="2">
+      <t>ジョサン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>乗算</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウザン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>正の整数同士</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>結果が負の数</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>小数を含む</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>割り切れる</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>割り切れない</t>
+    <rPh sb="0" eb="1">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0から引く</t>
+    <rPh sb="3" eb="4">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0を引く</t>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0を含む</t>
+    <rPh sb="2" eb="3">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0を割る</t>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>アプリを起動している状態</t>
+    <rPh sb="4" eb="6">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に20、演算記号に+を順番に入力し、それぞれEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に20、演算記号に-を順番に入力し、それぞれEnterを押下する</t>
+  </si>
+  <si>
+    <t>1つ目に1.5、2つ目に2、演算記号に*を順番に入力し、それぞれEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に2、演算記号に/を順番に入力し、それぞれEnterを押下する</t>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に3、演算記号に/を順番に入力し、それぞれEnterを押下する</t>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に0、演算記号に/を順番に入力し、それぞれEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に0、2つ目に20、演算記号に+を順番に入力し、それぞれEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に10、2つ目に0、演算記号に-を順番に入力し、それぞれEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>1つ目に0、2つ目に10、演算記号に-を順番に入力し、それぞれEnterを押下する</t>
+  </si>
+  <si>
+    <t>1つ目に0、2つ目に10、演算記号に/を順番に入力し、それぞれEnterを押下する</t>
+  </si>
+  <si>
+    <t>計算結果「30」が表示される</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>計算結果「3」が表示される</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>計算結果「5」が表示される</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>計算結果「3.33」が表示される（小数点第2位まで表示する仕様の場合）</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>エラーメッセージが表示される（内容は要確認）</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>計算結果「0」が表示される</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>乗算</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0を含む</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0で割る</t>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つ目に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つ目に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、演算記号に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を順番に入力し、それぞれ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を押下する</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計算結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」が表示される</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計算結果「-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」が表示される</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計算結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」が表示される</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>計算結果「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」が表示される</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>消費税計算</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>税率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>％</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ゼイリツ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>税率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <t>正の整数</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0円</t>
+  </si>
+  <si>
+    <t>端数が出る金額</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>負の金額</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>文字入力</t>
+  </si>
+  <si>
+    <t>未入力</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>アプリを起動し、消費税計算機能を選択している状態</t>
+  </si>
+  <si>
+    <t>税抜金額に1000を入力し、Enterを押下する</t>
+  </si>
+  <si>
+    <t>税抜金額に0を入力し、Enterを押下する</t>
+  </si>
+  <si>
+    <t>税抜金額に105を入力し、Enterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>税抜金額に-100を入力し、Enterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>税抜金額にabcを入力し、Enterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>金額を入力せずにEnterを押下する</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>税込金額「1100円」が表示される</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>税込金額「0円」が表示される</t>
+  </si>
+  <si>
+    <t>税込金額「116円」が表示される（1円未満を四捨五入する場合）</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示され、再入力を求められる（負の金額を禁止する場合）</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="'Microsoft Sans Serif'"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="'Microsoft Sans Serif'"/>
     </font>
-    <font/>
     <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -228,7 +946,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -237,8 +955,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
-    <border/>
+  <borders count="7">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="hair">
         <color rgb="FF000000"/>
@@ -252,6 +976,7 @@
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -263,6 +988,8 @@
       <top style="hair">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -271,6 +998,9 @@
       <right style="hair">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="hair">
@@ -279,70 +1009,125 @@
       <right style="hair">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="hair">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -532,36 +1317,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K1003"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.38"/>
-    <col customWidth="1" min="2" max="2" width="13.13"/>
-    <col customWidth="1" min="3" max="4" width="7.25"/>
-    <col customWidth="1" min="5" max="5" width="6.88"/>
-    <col customWidth="1" min="6" max="6" width="65.13"/>
-    <col customWidth="1" min="7" max="7" width="28.88"/>
-    <col customWidth="1" min="8" max="8" width="69.75"/>
-    <col customWidth="1" min="9" max="10" width="7.5"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="26" width="7.63"/>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="20.265625" customWidth="1"/>
+    <col min="3" max="3" width="9.265625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" customWidth="1"/>
+    <col min="5" max="5" width="6.86328125" customWidth="1"/>
+    <col min="6" max="6" width="65.1328125" customWidth="1"/>
+    <col min="7" max="7" width="33.33203125" customWidth="1"/>
+    <col min="8" max="8" width="91.796875" customWidth="1"/>
+    <col min="9" max="10" width="7.46484375" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="26" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" spans="1:11" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -570,13 +1356,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -589,843 +1375,1187 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="5" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="5" t="s">
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="5" t="s">
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="4" t="s">
+      <c r="H5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="5" t="s">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="5" t="s">
+      <c r="H7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="A9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="4" t="s">
+      <c r="H8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="A10" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="5" t="s">
+      <c r="H9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="5" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="5" t="s">
+      <c r="H10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E11" s="4"/>
+      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="H11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7" t="s">
+      <c r="E12" s="4"/>
+      <c r="F12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="A13" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="5" t="s">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="A14" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="5" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="A15" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="A16" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="4" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+    </row>
+    <row r="35" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" ht="17.25" customHeight="1">
-      <c r="A17" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" ht="17.25" customHeight="1">
-      <c r="A18" s="3">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" ht="17.25" customHeight="1">
-      <c r="A19" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" ht="17.25" customHeight="1">
-      <c r="A20" s="3">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" ht="17.25" customHeight="1">
-      <c r="A21" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" ht="17.25" customHeight="1">
-      <c r="A22" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="B44" s="13"/>
+      <c r="C44" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="B45" s="13"/>
+      <c r="C45" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7" t="s">
+      <c r="B46" s="13"/>
+      <c r="C46" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="B47" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="B48" s="26"/>
+      <c r="C48" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" ht="17.25" customHeight="1">
-      <c r="A23" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="5" t="s">
+      <c r="B49" s="26"/>
+      <c r="C49" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="B50" s="26"/>
+      <c r="C50" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="B51" s="26"/>
+      <c r="C51" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" ht="17.25" customHeight="1">
-      <c r="A24" s="3">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" ht="17.25" customHeight="1">
-      <c r="A25" s="3">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" ht="17.25" customHeight="1">
-      <c r="A26" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" ht="17.25" customHeight="1">
-      <c r="A27" s="3">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" ht="17.25" customHeight="1">
-      <c r="A30" s="3">
-        <v>29.0</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" ht="17.25" customHeight="1">
-      <c r="A31" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" ht="17.25" customHeight="1">
-      <c r="A32" s="3">
-        <v>31.0</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" ht="17.25" customHeight="1">
-      <c r="A33" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34" ht="17.25" customHeight="1">
-      <c r="A34" s="3">
-        <v>33.0</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35" ht="17.25" customHeight="1">
-      <c r="A35" s="3">
-        <v>34.0</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36" ht="17.25" customHeight="1"/>
-    <row r="37" ht="17.25" customHeight="1"/>
-    <row r="38" ht="17.25" customHeight="1"/>
-    <row r="39" ht="17.25" customHeight="1"/>
-    <row r="40" ht="17.25" customHeight="1"/>
-    <row r="41" ht="17.25" customHeight="1"/>
-    <row r="42" ht="17.25" customHeight="1"/>
-    <row r="43" ht="17.25" customHeight="1"/>
-    <row r="44" ht="17.25" customHeight="1"/>
-    <row r="45" ht="17.25" customHeight="1"/>
-    <row r="46" ht="17.25" customHeight="1"/>
-    <row r="47" ht="17.25" customHeight="1"/>
-    <row r="48" ht="17.25" customHeight="1"/>
-    <row r="49" ht="17.25" customHeight="1"/>
-    <row r="50" ht="17.25" customHeight="1"/>
-    <row r="51" ht="17.25" customHeight="1"/>
-    <row r="52" ht="17.25" customHeight="1"/>
-    <row r="53" ht="17.25" customHeight="1"/>
-    <row r="54" ht="17.25" customHeight="1"/>
-    <row r="55" ht="17.25" customHeight="1"/>
-    <row r="56" ht="17.25" customHeight="1"/>
-    <row r="57" ht="17.25" customHeight="1"/>
-    <row r="58" ht="17.25" customHeight="1"/>
-    <row r="59" ht="17.25" customHeight="1"/>
-    <row r="60" ht="17.25" customHeight="1"/>
-    <row r="61" ht="17.25" customHeight="1"/>
-    <row r="62" ht="17.25" customHeight="1"/>
-    <row r="63" ht="17.25" customHeight="1"/>
-    <row r="64" ht="17.25" customHeight="1"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="54" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="55" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="56" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="57" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="58" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="59" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="60" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="61" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="62" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="63" spans="1:8" ht="17.25" customHeight="1"/>
+    <row r="64" spans="1:8" ht="17.25" customHeight="1"/>
     <row r="65" ht="17.25" customHeight="1"/>
     <row r="66" ht="17.25" customHeight="1"/>
     <row r="67" ht="17.25" customHeight="1"/>
@@ -2362,8 +3492,13 @@
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
+    <row r="1001" ht="17.25" customHeight="1"/>
+    <row r="1002" ht="17.25" customHeight="1"/>
+    <row r="1003" ht="17.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="B36:B46"/>
+    <mergeCell ref="B47:B52"/>
     <mergeCell ref="B12:B21"/>
     <mergeCell ref="B22:B35"/>
     <mergeCell ref="B2:B11"/>
@@ -2378,21 +3513,18 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C33:C35"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A1000"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="7.63"/>
+    <col min="1" max="26" width="7.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1"/>
@@ -3396,9 +4528,8 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>